--- a/W1_sdm_impacts.xlsx
+++ b/W1_sdm_impacts.xlsx
@@ -474,40 +474,40 @@
         <v>13</v>
       </c>
       <c r="B2">
-        <v>0.0102038475398559</v>
+        <v>-0.009163197276475011</v>
       </c>
       <c r="C2">
-        <v>0.03846073424269339</v>
+        <v>0.04873465834945671</v>
       </c>
       <c r="D2">
-        <v>0.04866458178254929</v>
+        <v>0.0395714610729817</v>
       </c>
       <c r="E2">
-        <v>0.04441413294696103</v>
+        <v>0.03902261880128532</v>
       </c>
       <c r="F2">
-        <v>0.2297432565449662</v>
+        <v>-0.2348175893354753</v>
       </c>
       <c r="G2">
-        <v>0.818291279947124</v>
+        <v>0.8143503150882592</v>
       </c>
       <c r="H2">
-        <v>0.1125872447867056</v>
+        <v>0.08992972983729391</v>
       </c>
       <c r="I2">
-        <v>0.3416082729047727</v>
+        <v>0.5419193234276394</v>
       </c>
       <c r="J2">
-        <v>0.7326457104953517</v>
+        <v>0.5878740844000006</v>
       </c>
       <c r="K2">
-        <v>0.1457279845075649</v>
+        <v>0.1185747416391998</v>
       </c>
       <c r="L2">
-        <v>0.3339412258187311</v>
+        <v>0.3337258890547709</v>
       </c>
       <c r="M2">
-        <v>0.7384239100174017</v>
+        <v>0.7385864118647976</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -515,40 +515,40 @@
         <v>14</v>
       </c>
       <c r="B3">
-        <v>-0.3568296508325117</v>
+        <v>-0.5903304530701048</v>
       </c>
       <c r="C3">
-        <v>1.490360715969296</v>
+        <v>1.960213845422615</v>
       </c>
       <c r="D3">
-        <v>1.133531065136784</v>
+        <v>1.36988339235251</v>
       </c>
       <c r="E3">
-        <v>0.4888136617784019</v>
+        <v>0.4108516839317378</v>
       </c>
       <c r="F3">
-        <v>-0.729991157641327</v>
+        <v>-1.436845645661725</v>
       </c>
       <c r="G3">
-        <v>0.4653955895535986</v>
+        <v>0.1507618571944136</v>
       </c>
       <c r="H3">
-        <v>1.123536902052712</v>
+        <v>0.8002109787083421</v>
       </c>
       <c r="I3">
-        <v>1.326490223192842</v>
+        <v>2.449621284360142</v>
       </c>
       <c r="J3">
-        <v>0.1846773714248342</v>
+        <v>0.01430065387576174</v>
       </c>
       <c r="K3">
-        <v>1.473706128459773</v>
+        <v>1.072929039601844</v>
       </c>
       <c r="L3">
-        <v>0.7691703544189512</v>
+        <v>1.27676979724667</v>
       </c>
       <c r="M3">
-        <v>0.4417921869132229</v>
+        <v>0.2016835314554655</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -556,40 +556,40 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>0.1181557839287786</v>
+        <v>0.04851923402593315</v>
       </c>
       <c r="C4">
-        <v>0.1789463247374581</v>
+        <v>-0.02116267893616833</v>
       </c>
       <c r="D4">
-        <v>0.2971021086662367</v>
+        <v>0.02735655508976481</v>
       </c>
       <c r="E4">
-        <v>0.05020006130382431</v>
+        <v>0.02891202682449865</v>
       </c>
       <c r="F4">
-        <v>2.353698000758762</v>
+        <v>1.678167854521368</v>
       </c>
       <c r="G4">
-        <v>0.01858770558815825</v>
+        <v>0.09331433523961441</v>
       </c>
       <c r="H4">
-        <v>0.162814377629353</v>
+        <v>0.08535436871534668</v>
       </c>
       <c r="I4">
-        <v>1.099081833822008</v>
+        <v>-0.2479390247351603</v>
       </c>
       <c r="J4">
-        <v>0.2717323729273549</v>
+        <v>0.8041815850294982</v>
       </c>
       <c r="K4">
-        <v>0.210198143706246</v>
+        <v>0.1123127363300291</v>
       </c>
       <c r="L4">
-        <v>1.413438308386966</v>
+        <v>0.2435748249368445</v>
       </c>
       <c r="M4">
-        <v>0.1575268884960472</v>
+        <v>0.8075601279193261</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -597,40 +597,40 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>-3.266015831181129</v>
+        <v>-2.96647469390945</v>
       </c>
       <c r="C5">
-        <v>-13.12116279565189</v>
+        <v>-13.02846962829918</v>
       </c>
       <c r="D5">
-        <v>-16.38717862683302</v>
+        <v>-15.99494432220863</v>
       </c>
       <c r="E5">
-        <v>2.227535560700217</v>
+        <v>1.820160594844247</v>
       </c>
       <c r="F5">
-        <v>-1.46620143301078</v>
+        <v>-1.629787339816185</v>
       </c>
       <c r="G5">
-        <v>0.142593418334038</v>
+        <v>0.1031464504285395</v>
       </c>
       <c r="H5">
-        <v>6.00140539201191</v>
+        <v>4.514744825956496</v>
       </c>
       <c r="I5">
-        <v>-2.186348353190177</v>
+        <v>-2.88575991125677</v>
       </c>
       <c r="J5">
-        <v>0.02879012907467615</v>
+        <v>0.003904699018039581</v>
       </c>
       <c r="K5">
-        <v>8.024434238350068</v>
+        <v>6.13193312749379</v>
       </c>
       <c r="L5">
-        <v>-2.042160000329499</v>
+        <v>-2.608466855336695</v>
       </c>
       <c r="M5">
-        <v>0.04113566278023106</v>
+        <v>0.009094881904408991</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -638,40 +638,40 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>-16.16084818304979</v>
+        <v>4.593168875787192</v>
       </c>
       <c r="C6">
-        <v>-53.95081880975569</v>
+        <v>30.07850181268388</v>
       </c>
       <c r="D6">
-        <v>-70.11166699280548</v>
+        <v>34.67167068847107</v>
       </c>
       <c r="E6">
-        <v>29.28198976636356</v>
+        <v>19.44315328417856</v>
       </c>
       <c r="F6">
-        <v>-0.5519040308392527</v>
+        <v>0.2362358002662451</v>
       </c>
       <c r="G6">
-        <v>0.5810141065815473</v>
+        <v>0.8132497009565447</v>
       </c>
       <c r="H6">
-        <v>97.68235037324436</v>
+        <v>55.09979230402613</v>
       </c>
       <c r="I6">
-        <v>-0.5523087702497897</v>
+        <v>0.5458913827972097</v>
       </c>
       <c r="J6">
-        <v>0.5807368228362662</v>
+        <v>0.5851406021086114</v>
       </c>
       <c r="K6">
-        <v>123.8026179752666</v>
+        <v>71.62625711127083</v>
       </c>
       <c r="L6">
-        <v>-0.5663181291272243</v>
+        <v>0.4840636951698998</v>
       </c>
       <c r="M6">
-        <v>0.571177538557706</v>
+        <v>0.6283406656462116</v>
       </c>
     </row>
   </sheetData>
